--- a/Lab3Analysis/results.xlsx
+++ b/Lab3Analysis/results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/15f62b55ae07b806/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Coding\COP3503C\Lab3Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="8_{E03566BF-D216-48FD-8C16-A98E45CC07B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C8868FF-2185-47AD-9ABD-0CB3F79C4C5E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1F545A-56F1-4E76-B4C0-41EB81D347AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5F0913F3-B6AB-45BE-945A-6C3D7068312E}"/>
   </bookViews>
@@ -26,10 +26,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -115,7 +115,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1022,6 +1022,64 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>ABS Scale Factor 1.5: Push resizes = 45, Pop resizes = 90</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1163,7 +1221,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1171,6 +1228,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1569,6 +1627,64 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>ABQ Scale Factor 2.0: Enqueue resizes = 26, Dequeue resizes = 53</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1710,7 +1826,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1718,6 +1833,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2116,6 +2232,64 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>ABS Scale Factor 2.0: Push resizes = 26, Pop resizes = 53</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2257,7 +2431,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2265,6 +2438,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2663,6 +2837,64 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>ABS Scale Factor 3.0: Push resizes = 17, Pop resizes = 35</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2804,7 +3036,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2812,6 +3043,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3210,6 +3442,64 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>ABS Scale Factor 10.0: Push resizes = 8, Pop resizes = 17</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3351,7 +3641,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3359,6 +3648,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3757,6 +4047,64 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>ABS Scale Factor 100.0: Push resizes = 4, Pop resizes = 9</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3898,7 +4246,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3906,6 +4253,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4304,6 +4652,64 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>ABQ Scale Factor 1.5: Enqueue resizes = 45, Dequeue resizes = 90</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -4445,7 +4851,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4453,6 +4858,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4851,6 +5257,64 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>ABQ Scale Factor 3.0: Enqueue resizes = 17, Dequeue resizes = 35</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -4992,7 +5456,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5000,6 +5463,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5398,6 +5862,64 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>ABQ Scale Factor 10.0: Enqueue resizes = 8, Dequeue resizes = 17</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -5539,7 +6061,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5547,6 +6068,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5945,6 +6467,64 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>ABQ Scale Factor 100.0: Enqueue resizes = 4, Dequeue resizes = 9</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -6086,7 +6666,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6094,6 +6673,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -12375,15 +12955,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E64FBB6-25AC-449D-8947-8B296643C541}">
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12400,7 +12980,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -12417,7 +12997,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -12434,7 +13014,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -12451,7 +13031,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -12468,7 +13048,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -12485,7 +13065,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -12502,7 +13082,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -12519,7 +13099,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -12536,7 +13116,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -12553,7 +13133,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -12570,7 +13150,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -12587,7 +13167,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -12604,7 +13184,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -12621,7 +13201,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -12638,7 +13218,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -12655,7 +13235,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -12672,7 +13252,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -12689,7 +13269,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -12706,7 +13286,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -12723,7 +13303,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -12740,7 +13320,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -12757,7 +13337,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -12774,7 +13354,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -12791,7 +13371,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -12808,7 +13388,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -12825,7 +13405,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -12842,7 +13422,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -12859,7 +13439,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -12876,7 +13456,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -12893,7 +13473,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -12910,7 +13490,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -12927,7 +13507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>8</v>
       </c>
@@ -12944,7 +13524,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -12961,7 +13541,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -12978,7 +13558,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -12995,7 +13575,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -13012,7 +13592,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -13029,7 +13609,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -13046,7 +13626,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -13063,7 +13643,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -13080,7 +13660,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -13097,7 +13677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -13114,7 +13694,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -13131,7 +13711,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>8</v>
       </c>
@@ -13148,7 +13728,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -13165,7 +13745,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -13182,7 +13762,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -13199,7 +13779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -13216,7 +13796,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -13233,7 +13813,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -13250,7 +13830,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -13267,7 +13847,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -13284,7 +13864,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -13301,7 +13881,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -13318,7 +13898,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -13335,7 +13915,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -13352,7 +13932,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -13369,7 +13949,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -13386,7 +13966,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -13403,7 +13983,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>8</v>
       </c>
@@ -13420,7 +14000,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -13437,7 +14017,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -13454,7 +14034,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -13471,7 +14051,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>8</v>
       </c>
@@ -13488,7 +14068,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -13505,7 +14085,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -13522,7 +14102,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -13539,7 +14119,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>8</v>
       </c>
@@ -13556,7 +14136,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>5</v>
       </c>
@@ -13573,7 +14153,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -13590,7 +14170,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -13607,7 +14187,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>8</v>
       </c>
@@ -13624,7 +14204,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>5</v>
       </c>
@@ -13641,7 +14221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>6</v>
       </c>
@@ -13658,7 +14238,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -13675,7 +14255,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -13692,7 +14272,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -13709,7 +14289,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -13726,7 +14306,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>7</v>
       </c>
@@ -13743,7 +14323,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>8</v>
       </c>
@@ -13760,7 +14340,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>5</v>
       </c>
@@ -13777,7 +14357,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>6</v>
       </c>
@@ -13794,7 +14374,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>7</v>
       </c>
@@ -13811,7 +14391,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -13828,7 +14408,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>5</v>
       </c>
@@ -13845,7 +14425,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>6</v>
       </c>
@@ -13862,7 +14442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>7</v>
       </c>
@@ -13879,7 +14459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
         <v>8</v>
       </c>
@@ -13896,7 +14476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>5</v>
       </c>
@@ -13913,7 +14493,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
         <v>6</v>
       </c>
@@ -13930,7 +14510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
         <v>7</v>
       </c>
@@ -13947,7 +14527,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -13964,7 +14544,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
         <v>5</v>
       </c>
@@ -13981,7 +14561,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -13998,7 +14578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
         <v>7</v>
       </c>
@@ -14015,7 +14595,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
         <v>8</v>
       </c>
@@ -14032,7 +14612,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
         <v>5</v>
       </c>
@@ -14049,7 +14629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
         <v>6</v>
       </c>
@@ -14066,7 +14646,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
         <v>7</v>
       </c>
@@ -14083,7 +14663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -14109,19 +14689,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BF0C1F-A754-415C-A443-CE584771C95E}">
   <dimension ref="A1:C150"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -14132,7 +14712,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>10000000</v>
       </c>
@@ -14143,7 +14723,7 @@
         <v>0.173572</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>30000000</v>
       </c>
@@ -14154,7 +14734,7 @@
         <v>0.55316799999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>50000000</v>
       </c>
@@ -14165,7 +14745,7 @@
         <v>0.85628400000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>75000000</v>
       </c>
@@ -14176,7 +14756,7 @@
         <v>1.29596</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>100000000</v>
       </c>
@@ -14187,14 +14767,14 @@
         <v>1.8413999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -14205,7 +14785,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>10000000</v>
       </c>
@@ -14216,7 +14796,7 @@
         <v>0.144261</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>30000000</v>
       </c>
@@ -14227,7 +14807,7 @@
         <v>0.36504700000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>50000000</v>
       </c>
@@ -14238,7 +14818,7 @@
         <v>0.705183</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>75000000</v>
       </c>
@@ -14249,7 +14829,7 @@
         <v>1.11677</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>100000000</v>
       </c>
@@ -14260,14 +14840,14 @@
         <v>1.3060799999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -14278,7 +14858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34">
         <v>10000000</v>
       </c>
@@ -14289,7 +14869,7 @@
         <v>0.13797400000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35">
         <v>30000000</v>
       </c>
@@ -14300,7 +14880,7 @@
         <v>0.41410799999999998</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36">
         <v>50000000</v>
       </c>
@@ -14311,7 +14891,7 @@
         <v>0.562442</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37">
         <v>75000000</v>
       </c>
@@ -14322,7 +14902,7 @@
         <v>0.75284600000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38">
         <v>100000000</v>
       </c>
@@ -14333,14 +14913,14 @@
         <v>1.3475900000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="A48" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -14351,7 +14931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50">
         <v>10000000</v>
       </c>
@@ -14362,7 +14942,7 @@
         <v>8.9852299999999996E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3">
       <c r="A51">
         <v>30000000</v>
       </c>
@@ -14373,7 +14953,7 @@
         <v>0.45527600000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3">
       <c r="A52">
         <v>50000000</v>
       </c>
@@ -14384,7 +14964,7 @@
         <v>0.56084100000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3">
       <c r="A53">
         <v>75000000</v>
       </c>
@@ -14395,7 +14975,7 @@
         <v>0.73769700000000005</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3">
       <c r="A54">
         <v>100000000</v>
       </c>
@@ -14406,14 +14986,14 @@
         <v>0.91934099999999996</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="A64" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -14424,7 +15004,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3">
       <c r="A66">
         <v>10000000</v>
       </c>
@@ -14435,7 +15015,7 @@
         <v>0.144429</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3">
       <c r="A67">
         <v>30000000</v>
       </c>
@@ -14446,7 +15026,7 @@
         <v>0.29740800000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3">
       <c r="A68">
         <v>50000000</v>
       </c>
@@ -14457,7 +15037,7 @@
         <v>0.44908500000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3">
       <c r="A69">
         <v>75000000</v>
       </c>
@@ -14468,7 +15048,7 @@
         <v>0.63973100000000005</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3">
       <c r="A70">
         <v>100000000</v>
       </c>
@@ -14479,14 +15059,14 @@
         <v>0.90110199999999996</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3">
       <c r="A80" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -14497,7 +15077,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3">
       <c r="A82">
         <v>10000000</v>
       </c>
@@ -14508,7 +15088,7 @@
         <v>0.15831799999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3">
       <c r="A83">
         <v>30000000</v>
       </c>
@@ -14519,7 +15099,7 @@
         <v>0.48785099999999998</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3">
       <c r="A84">
         <v>50000000</v>
       </c>
@@ -14530,7 +15110,7 @@
         <v>0.729217</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3">
       <c r="A85">
         <v>75000000</v>
       </c>
@@ -14541,7 +15121,7 @@
         <v>1.2423200000000001</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3">
       <c r="A86">
         <v>100000000</v>
       </c>
@@ -14552,12 +15132,12 @@
         <v>1.4371700000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3">
       <c r="A96" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3">
       <c r="A97" t="s">
         <v>11</v>
       </c>
@@ -14568,7 +15148,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3">
       <c r="A98">
         <v>10000000</v>
       </c>
@@ -14579,7 +15159,7 @@
         <v>0.15831799999999999</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3">
       <c r="A99">
         <v>30000000</v>
       </c>
@@ -14590,7 +15170,7 @@
         <v>0.48785099999999998</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3">
       <c r="A100">
         <v>50000000</v>
       </c>
@@ -14601,7 +15181,7 @@
         <v>0.729217</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3">
       <c r="A101">
         <v>75000000</v>
       </c>
@@ -14612,7 +15192,7 @@
         <v>1.2423200000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3">
       <c r="A102">
         <v>100000000</v>
       </c>
@@ -14623,14 +15203,14 @@
         <v>1.4371700000000001</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3">
       <c r="A112" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3">
       <c r="A113" t="s">
         <v>11</v>
       </c>
@@ -14641,7 +15221,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3">
       <c r="A114">
         <v>10000000</v>
       </c>
@@ -14652,7 +15232,7 @@
         <v>0.15427199999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3">
       <c r="A115">
         <v>30000000</v>
       </c>
@@ -14663,7 +15243,7 @@
         <v>0.453762</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3">
       <c r="A116">
         <v>50000000</v>
       </c>
@@ -14674,7 +15254,7 @@
         <v>0.62549500000000002</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3">
       <c r="A117">
         <v>75000000</v>
       </c>
@@ -14685,7 +15265,7 @@
         <v>0.84069199999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3">
       <c r="A118">
         <v>100000000</v>
       </c>
@@ -14696,14 +15276,14 @@
         <v>1.58595</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3">
       <c r="A128" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3">
       <c r="A129" t="s">
         <v>11</v>
       </c>
@@ -14714,7 +15294,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3">
       <c r="A130">
         <v>10000000</v>
       </c>
@@ -14725,7 +15305,7 @@
         <v>0.100825</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3">
       <c r="A131">
         <v>30000000</v>
       </c>
@@ -14736,7 +15316,7 @@
         <v>0.45763700000000002</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3">
       <c r="A132">
         <v>50000000</v>
       </c>
@@ -14747,7 +15327,7 @@
         <v>0.60129500000000002</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3">
       <c r="A133">
         <v>75000000</v>
       </c>
@@ -14758,7 +15338,7 @@
         <v>0.819415</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3">
       <c r="A134">
         <v>100000000</v>
       </c>
@@ -14769,14 +15349,14 @@
         <v>1.0241899999999999</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3">
       <c r="A144" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3">
       <c r="A145" t="s">
         <v>11</v>
       </c>
@@ -14787,7 +15367,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3">
       <c r="A146">
         <v>10000000</v>
       </c>
@@ -14798,7 +15378,7 @@
         <v>0.16547000000000001</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3">
       <c r="A147">
         <v>30000000</v>
       </c>
@@ -14809,7 +15389,7 @@
         <v>0.32722499999999999</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3">
       <c r="A148">
         <v>50000000</v>
       </c>
@@ -14820,7 +15400,7 @@
         <v>0.50281600000000004</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3">
       <c r="A149">
         <v>75000000</v>
       </c>
@@ -14831,7 +15411,7 @@
         <v>0.73376200000000003</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3">
       <c r="A150">
         <v>100000000</v>
       </c>

--- a/Lab3Analysis/results.xlsx
+++ b/Lab3Analysis/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Coding\COP3503C\Lab3Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1F545A-56F1-4E76-B4C0-41EB81D347AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0551BD31-22D6-4099-8AA6-2E40D4AEC996}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5F0913F3-B6AB-45BE-945A-6C3D7068312E}"/>
   </bookViews>
@@ -20,24 +20,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">results!$A$1:$E$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="25">
   <si>
     <t>Task</t>
   </si>
@@ -109,6 +96,9 @@
   </si>
   <si>
     <t>ABQ Scale Factor 2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -4423,19 +4413,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.15773999999999999</c:v>
+                  <c:v>0.18937399999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.43924600000000003</c:v>
+                  <c:v>0.59200299999999995</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.72861399999999998</c:v>
+                  <c:v>0.92942999999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.2102999999999999</c:v>
+                  <c:v>1.37951</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.4164000000000001</c:v>
+                  <c:v>1.9923999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4504,19 +4494,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.15831799999999999</c:v>
+                  <c:v>0.19003100000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.48785099999999998</c:v>
+                  <c:v>0.59532300000000005</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.729217</c:v>
+                  <c:v>0.93585799999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.2423200000000001</c:v>
+                  <c:v>1.3950899999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.4371700000000001</c:v>
+                  <c:v>1.9825999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14688,7 +14678,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BF0C1F-A754-415C-A443-CE584771C95E}">
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="10" bestFit="1" customWidth="1"/>
@@ -14774,7 +14764,7 @@
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -14785,7 +14775,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>10000000</v>
       </c>
@@ -14796,7 +14786,7 @@
         <v>0.144261</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>30000000</v>
       </c>
@@ -14807,7 +14797,7 @@
         <v>0.36504700000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>50000000</v>
       </c>
@@ -14818,7 +14808,7 @@
         <v>0.705183</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>75000000</v>
       </c>
@@ -14829,7 +14819,7 @@
         <v>1.11677</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>100000000</v>
       </c>
@@ -14840,7 +14830,12 @@
         <v>1.3060799999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="24" spans="1:4">
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
         <v>16</v>
       </c>
@@ -15082,10 +15077,10 @@
         <v>10000000</v>
       </c>
       <c r="B82">
-        <v>0.15773999999999999</v>
+        <v>0.18937399999999999</v>
       </c>
       <c r="C82">
-        <v>0.15831799999999999</v>
+        <v>0.19003100000000001</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -15093,10 +15088,10 @@
         <v>30000000</v>
       </c>
       <c r="B83">
-        <v>0.43924600000000003</v>
+        <v>0.59200299999999995</v>
       </c>
       <c r="C83">
-        <v>0.48785099999999998</v>
+        <v>0.59532300000000005</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -15104,10 +15099,10 @@
         <v>50000000</v>
       </c>
       <c r="B84">
-        <v>0.72861399999999998</v>
+        <v>0.92942999999999998</v>
       </c>
       <c r="C84">
-        <v>0.729217</v>
+        <v>0.93585799999999997</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -15115,10 +15110,10 @@
         <v>75000000</v>
       </c>
       <c r="B85">
-        <v>1.2102999999999999</v>
+        <v>1.37951</v>
       </c>
       <c r="C85">
-        <v>1.2423200000000001</v>
+        <v>1.3950899999999999</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -15126,10 +15121,10 @@
         <v>100000000</v>
       </c>
       <c r="B86">
-        <v>1.4164000000000001</v>
+        <v>1.9923999999999999</v>
       </c>
       <c r="C86">
-        <v>1.4371700000000001</v>
+        <v>1.9825999999999999</v>
       </c>
     </row>
     <row r="96" spans="1:3">
